--- a/data.xlsx
+++ b/data.xlsx
@@ -32,10 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -66,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,378 +397,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
+      <c r="A1" t="str">
         <v>fecha</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" t="str">
         <v>CFVELEZM_pts</v>
       </c>
-      <c r="C1" s="1" t="str">
+      <c r="C1" t="str">
         <v>CFVELEZM_pl</v>
       </c>
-      <c r="D1" s="1" t="str">
+      <c r="D1" t="str">
         <v>ALEJANDRO_P_pts</v>
       </c>
-      <c r="E1" s="1" t="str">
+      <c r="E1" t="str">
         <v>ALEJANDRO_P_pl</v>
       </c>
-      <c r="F1" s="1" t="str">
+      <c r="F1" t="str">
         <v>ALEJANDRO_N_pts</v>
       </c>
-      <c r="G1" s="1" t="str">
+      <c r="G1" t="str">
         <v>ALEJANDRO_N_pl</v>
       </c>
-      <c r="H1" s="1" t="str">
+      <c r="H1" t="str">
         <v>ULIOCES_pts</v>
       </c>
-      <c r="I1" s="1" t="str">
+      <c r="I1" t="str">
         <v>ULIOCES_pl</v>
       </c>
-      <c r="J1" s="1" t="str">
+      <c r="J1" t="str">
         <v>ALEJANDRO_S_pts</v>
       </c>
-      <c r="K1" s="1" t="str">
+      <c r="K1" t="str">
         <v>ALEJANDRO_S_pl</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="str">
+      <c r="A2" t="str">
         <v>18/06</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" t="str">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" t="str">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="str">
+      <c r="E2" t="str">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="str">
+      <c r="F2" t="str">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="str">
+      <c r="G2" t="str">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="str">
+      <c r="H2" t="str">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="str">
+      <c r="I2" t="str">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="str">
+      <c r="J2" t="str">
         <v>5</v>
       </c>
-      <c r="K2" s="1" t="str">
+      <c r="K2" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="str">
+      <c r="A3" t="str">
         <v>19/06</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>22</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>18</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="str">
+      <c r="G3" t="str">
         <v>1</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3">
         <v>16</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3">
         <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="str">
+      <c r="A4" t="str">
         <v>22/06</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>61</v>
       </c>
-      <c r="C4" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="C4" t="str">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>48</v>
       </c>
-      <c r="E4" s="1" t="str">
+      <c r="E4" t="str">
         <v>1</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>49</v>
       </c>
-      <c r="G4" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="G4" t="str">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>49</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4">
         <v>27</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="str">
+      <c r="A5" t="str">
         <v>23/06</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>74</v>
       </c>
-      <c r="C5" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" t="str">
+        <v>2</v>
+      </c>
+      <c r="D5">
         <v>56</v>
       </c>
-      <c r="E5" s="1" t="str">
+      <c r="E5" t="str">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>62</v>
       </c>
-      <c r="G5" s="1" t="str">
+      <c r="G5" t="str">
         <v>3</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>65</v>
       </c>
-      <c r="I5" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="I5" t="str">
+        <v>2</v>
+      </c>
+      <c r="J5">
         <v>39</v>
       </c>
-      <c r="K5" s="1" t="str">
+      <c r="K5" t="str">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="str">
+      <c r="A6" t="str">
         <v>24/06</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>86</v>
       </c>
-      <c r="C6" s="1" t="str">
+      <c r="C6" t="str">
         <v>3</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>68</v>
       </c>
-      <c r="E6" s="1" t="str">
+      <c r="E6" t="str">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>73</v>
       </c>
-      <c r="G6" s="1" t="str">
+      <c r="G6" t="str">
         <v>3</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>76</v>
       </c>
-      <c r="I6" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="I6" t="str">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>53</v>
       </c>
-      <c r="K6" s="1" t="str">
+      <c r="K6" t="str">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="str">
+      <c r="A7" t="str">
         <v>25/06</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>105</v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C7" t="str">
         <v>5</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>84</v>
       </c>
-      <c r="E7" s="1" t="str">
+      <c r="E7" t="str">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>87</v>
       </c>
-      <c r="G7" s="1" t="str">
+      <c r="G7" t="str">
         <v>3</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>87</v>
       </c>
-      <c r="I7" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="I7" t="str">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>62</v>
       </c>
-      <c r="K7" s="1" t="str">
+      <c r="K7" t="str">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="str">
+      <c r="A8" t="str">
         <v>26/06</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>115</v>
       </c>
-      <c r="C8" s="1" t="str">
+      <c r="C8" t="str">
         <v>5</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>98</v>
       </c>
-      <c r="E8" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8">
         <v>97</v>
       </c>
-      <c r="G8" s="1" t="str">
+      <c r="G8" t="str">
         <v>3</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>98</v>
       </c>
-      <c r="I8" s="1" t="str">
+      <c r="I8" t="str">
         <v>3</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8">
         <v>67</v>
       </c>
-      <c r="K8" s="1" t="str">
+      <c r="K8" t="str">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="str">
+      <c r="A9" t="str">
         <v>29/06</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>146</v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C9" t="str">
         <v>5</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>133</v>
       </c>
-      <c r="E9" s="1" t="str">
+      <c r="E9" t="str">
         <v>4</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>129</v>
       </c>
-      <c r="G9" s="1" t="str">
+      <c r="G9" t="str">
         <v>4</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>134</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="I9" t="str">
         <v>5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9">
         <v>93</v>
       </c>
-      <c r="K9" s="1" t="str">
+      <c r="K9" t="str">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="str">
+      <c r="A10" t="str">
         <v>30/06</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>154</v>
       </c>
-      <c r="C10" s="1" t="str">
+      <c r="C10" t="str">
         <v>6</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>136</v>
       </c>
-      <c r="E10" s="1" t="str">
+      <c r="E10" t="str">
         <v>4</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>135</v>
       </c>
-      <c r="G10" s="1" t="str">
+      <c r="G10" t="str">
         <v>5</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>140</v>
       </c>
-      <c r="I10" s="1" t="str">
+      <c r="I10" t="str">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>93</v>
       </c>
-      <c r="K10" s="1" t="str">
+      <c r="K10" t="str">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="str">
+      <c r="A11" t="str">
         <v>01/07</v>
       </c>
-      <c r="B11" s="1" t="str">
+      <c r="B11" t="str">
         <v>164</v>
       </c>
-      <c r="C11" s="1" t="str">
+      <c r="C11" t="str">
         <v>8</v>
       </c>
-      <c r="D11" s="1" t="str">
+      <c r="D11" t="str">
         <v>148</v>
       </c>
-      <c r="E11" s="1" t="str">
+      <c r="E11" t="str">
         <v>4</v>
       </c>
-      <c r="F11" s="1" t="str">
+      <c r="F11" t="str">
         <v>149</v>
       </c>
-      <c r="G11" s="1" t="str">
+      <c r="G11" t="str">
         <v>7</v>
       </c>
-      <c r="H11" s="1" t="str">
+      <c r="H11" t="str">
         <v>149</v>
       </c>
-      <c r="I11" s="1" t="str">
+      <c r="I11" t="str">
         <v>7</v>
       </c>
-      <c r="J11" s="1" t="str">
+      <c r="J11" t="str">
         <v>100</v>
       </c>
-      <c r="K11" s="1" t="str">
+      <c r="K11" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>02/07</v>
+      </c>
+      <c r="B12" t="str">
+        <v>173</v>
+      </c>
+      <c r="C12" t="str">
+        <v>8</v>
+      </c>
+      <c r="D12" t="str">
+        <v>158</v>
+      </c>
+      <c r="E12" t="str">
+        <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>160</v>
+      </c>
+      <c r="G12" t="str">
+        <v>7</v>
+      </c>
+      <c r="H12" t="str">
+        <v>158</v>
+      </c>
+      <c r="I12" t="str">
+        <v>7</v>
+      </c>
+      <c r="J12" t="str">
+        <v>107</v>
+      </c>
+      <c r="K12" t="str">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>